--- a/data/trans_camb/IP19C08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 12,5</t>
+          <t>-3,59; 12,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; -1,14</t>
+          <t>-10,22; -1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 2,89</t>
+          <t>-7,99; 3,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 11,08</t>
+          <t>-3,49; 11,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 2,84</t>
+          <t>-6,97; 2,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 8,46</t>
+          <t>-3,12; 8,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,61</t>
+          <t>-1,55; 8,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,15</t>
+          <t>-6,57; 0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,54</t>
+          <t>-3,17; 4,8</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-97,5; 1024,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,65; —</t>
+          <t>-77,08; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 698,54</t>
+          <t>-38,24; 606,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,89; 345,53</t>
+          <t>-64,1; 403,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 2,5</t>
+          <t>-11,42; 3,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 5,97</t>
+          <t>-9,05; 5,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 4,26</t>
+          <t>-10,81; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 3,81</t>
+          <t>-11,48; 3,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -0,5</t>
+          <t>-14,74; -0,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -0,46</t>
+          <t>-15,99; -0,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 1,65</t>
+          <t>-8,45; 2,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 1,67</t>
+          <t>-8,83; 0,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 0,15</t>
+          <t>-9,62; 0,67</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 336,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-97,51; 423,97</t>
+          <t>-100,0; 335,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,26; 82,68</t>
+          <t>-85,67; 100,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,7; 105,53</t>
+          <t>-90,5; 86,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,97; 32,0</t>
+          <t>-91,36; 57,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 14,25</t>
+          <t>-1,24; 13,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,0</t>
+          <t>-7,67; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,87</t>
+          <t>-3,54; 6,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 2,19</t>
+          <t>-9,22; 2,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 6,9</t>
+          <t>-7,5; 6,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 7,8</t>
+          <t>-7,76; 7,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,96</t>
+          <t>-4,4; 5,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,04</t>
+          <t>-5,47; 3,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 5,5</t>
+          <t>-4,42; 5,44</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,54; 417,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 548,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,76; 382,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 0,13</t>
+          <t>-9,77; -0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,1</t>
+          <t>-7,17; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -1,0</t>
+          <t>-9,58; -0,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,45</t>
+          <t>-1,99; 6,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 7,68</t>
+          <t>-1,15; 8,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 15,83</t>
+          <t>-1,58; 14,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,85</t>
+          <t>-4,61; 2,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,56</t>
+          <t>-2,73; 4,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,35</t>
+          <t>-4,17; 6,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-92,32; 38,23</t>
+          <t>-93,11; 34,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 103,91</t>
+          <t>-69,98; 97,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,07</t>
+          <t>-94,22; 19,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-67,8; 596,54</t>
+          <t>-67,73; 769,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 764,21</t>
+          <t>-43,71; 956,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,26; —</t>
+          <t>-69,62; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,44; 65,32</t>
+          <t>-71,68; 67,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 154,99</t>
+          <t>-43,09; 149,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,06; 231,53</t>
+          <t>-71,93; 196,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 0,01</t>
+          <t>-15,54; 0,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 2,87</t>
+          <t>-14,14; 1,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,78; -1,47</t>
+          <t>-17,4; -0,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 6,78</t>
+          <t>-4,47; 7,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 0,0</t>
+          <t>-9,13; 0,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 0,14</t>
+          <t>-9,46; -0,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,82</t>
+          <t>-7,09; 1,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 0,21</t>
+          <t>-8,33; 0,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -1,55</t>
+          <t>-9,88; -1,56</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-94,88; 23,4</t>
+          <t>-93,11; 75,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,44; 85,63</t>
+          <t>-87,79; 68,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 404,22</t>
+          <t>-74,42; 517,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 59,6</t>
+          <t>-73,86; 66,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 25,29</t>
+          <t>-85,51; 32,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-95,08; -29,33</t>
+          <t>-94,67; -31,03</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 7,14</t>
+          <t>-9,85; 6,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 6,22</t>
+          <t>-8,83; 6,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -1,66</t>
+          <t>-13,97; -1,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-20,62; -2,38</t>
+          <t>-21,07; -2,21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,38; -1,58</t>
+          <t>-19,2; -1,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,99; -2,41</t>
+          <t>-21,51; -2,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -0,29</t>
+          <t>-12,43; -0,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 0,34</t>
+          <t>-11,35; 0,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -3,3</t>
+          <t>-13,85; -2,8</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,34</t>
+          <t>-100,0; 143,24</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,09</t>
+          <t>-100,0; 45,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,13</t>
+          <t>-94,57; 55,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -15,97</t>
+          <t>-100,0; -2,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,82</t>
+          <t>-4,56; 0,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,66</t>
+          <t>-4,85; 0,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -1,27</t>
+          <t>-6,36; -1,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,91</t>
+          <t>-3,11; 1,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 0,49</t>
+          <t>-4,24; 0,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,2</t>
+          <t>-4,0; 1,82</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,73</t>
+          <t>-3,28; 0,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,84; -0,27</t>
+          <t>-3,74; -0,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,4</t>
+          <t>-4,22; -0,46</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 21,07</t>
+          <t>-61,48; 21,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,68; 17,4</t>
+          <t>-64,93; 16,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,47; -25,2</t>
+          <t>-81,62; -23,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 55,21</t>
+          <t>-54,16; 49,46</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 16,43</t>
+          <t>-72,69; 14,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 74,55</t>
+          <t>-65,81; 60,26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 17,61</t>
+          <t>-51,63; 15,15</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-59,7; -5,95</t>
+          <t>-59,12; -5,77</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-69,03; -6,83</t>
+          <t>-66,26; -4,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 12,42</t>
+          <t>-3,7; 12,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -1,15</t>
+          <t>-11,09; -1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 3,48</t>
+          <t>-8,32; 3,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 11,47</t>
+          <t>-3,56; 10,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 2,87</t>
+          <t>-7,04; 2,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 8,69</t>
+          <t>-3,27; 8,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 8,6</t>
+          <t>-2,33; 9,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,16</t>
+          <t>-6,61; 0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,8</t>
+          <t>-3,99; 4,47</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-97,5; 1024,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 606,38</t>
+          <t>-60,46; 549,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 403,25</t>
+          <t>-72,75; 321,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 3,19</t>
+          <t>-10,85; 2,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 5,67</t>
+          <t>-9,02; 6,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 3,95</t>
+          <t>-11,14; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 3,74</t>
+          <t>-11,75; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -0,27</t>
+          <t>-14,34; -0,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,99; -0,64</t>
+          <t>-15,55; -0,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 2,03</t>
+          <t>-8,36; 1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 0,97</t>
+          <t>-9,03; 1,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,67</t>
+          <t>-8,91; 0,41</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 336,41</t>
+          <t>-100,0; 385,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 335,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 100,73</t>
+          <t>-89,76; 77,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,5; 86,52</t>
+          <t>-92,18; 65,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-91,36; 57,44</t>
+          <t>-90,32; 67,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 13,11</t>
+          <t>-1,22; 13,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,0</t>
+          <t>-7,6; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,29</t>
+          <t>-4,25; 5,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 2,05</t>
+          <t>-9,77; 1,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 6,87</t>
+          <t>-7,7; 6,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 7,45</t>
+          <t>-8,07; 7,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,26</t>
+          <t>-4,57; 5,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,2</t>
+          <t>-5,82; 3,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,44</t>
+          <t>-4,28; 5,08</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,36; 365,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 548,12</t>
+          <t>-100,0; 505,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,3; 449,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -0,24</t>
+          <t>-9,62; 0,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 3,55</t>
+          <t>-6,91; 4,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -0,39</t>
+          <t>-9,72; -0,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,63</t>
+          <t>-2,08; 6,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,21</t>
+          <t>-1,61; 7,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,36</t>
+          <t>-1,79; 14,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,1</t>
+          <t>-4,8; 1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,51</t>
+          <t>-2,77; 4,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,41</t>
+          <t>-4,26; 5,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-93,11; 34,88</t>
+          <t>-100,0; 37,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 97,81</t>
+          <t>-71,77; 102,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,22; 19,83</t>
+          <t>-92,46; 20,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 769,92</t>
+          <t>-65,24; 735,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,71; 956,47</t>
+          <t>-49,56; 791,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,62; —</t>
+          <t>-78,33; 1294,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 67,32</t>
+          <t>-72,23; 58,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 149,19</t>
+          <t>-42,72; 136,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 196,88</t>
+          <t>-73,25; 191,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 0,38</t>
+          <t>-15,28; 0,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 1,91</t>
+          <t>-12,8; 2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,4; -0,57</t>
+          <t>-16,17; -0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 7,16</t>
+          <t>-4,94; 6,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,03</t>
+          <t>-9,24; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -0,09</t>
+          <t>-9,85; -0,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,91</t>
+          <t>-7,39; 1,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 0,57</t>
+          <t>-8,62; 0,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -1,56</t>
+          <t>-9,54; -1,72</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-93,11; 75,71</t>
+          <t>-94,11; 34,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,79; 68,36</t>
+          <t>-89,73; 92,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 31,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,42; 517,93</t>
+          <t>-72,54; 471,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 114,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 66,61</t>
+          <t>-74,39; 53,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-85,51; 32,87</t>
+          <t>-86,67; 30,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-94,67; -31,03</t>
+          <t>-94,8; -31,08</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 6,62</t>
+          <t>-8,83; 7,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,48</t>
+          <t>-8,7; 6,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -1,65</t>
+          <t>-13,12; -1,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,07; -2,21</t>
+          <t>-20,98; -2,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -1,6</t>
+          <t>-20,75; 0,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,51; -2,87</t>
+          <t>-22,01; -2,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -0,16</t>
+          <t>-11,93; -0,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 0,36</t>
+          <t>-11,85; 0,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,85; -2,8</t>
+          <t>-14,34; -3,06</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 47,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,24</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,63</t>
+          <t>-100,0; 42,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-94,57; 55,98</t>
+          <t>-92,39; 51,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,95</t>
+          <t>-100,0; -17,99</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,78</t>
+          <t>-4,81; 0,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,62</t>
+          <t>-4,75; 0,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -1,15</t>
+          <t>-6,57; -1,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,65</t>
+          <t>-3,33; 1,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,42</t>
+          <t>-4,47; 0,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,82</t>
+          <t>-3,74; 2,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,65</t>
+          <t>-3,34; 0,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,32</t>
+          <t>-3,78; -0,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,46</t>
+          <t>-4,24; -0,37</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 21,46</t>
+          <t>-63,6; 21,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 16,33</t>
+          <t>-62,62; 19,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,62; -23,41</t>
+          <t>-81,63; -25,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 49,46</t>
+          <t>-54,99; 51,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,69; 14,27</t>
+          <t>-72,39; 9,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 60,26</t>
+          <t>-64,88; 60,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 15,15</t>
+          <t>-52,53; 12,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-59,12; -5,77</t>
+          <t>-59,48; -2,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,26; -4,34</t>
+          <t>-66,84; -3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 12,89</t>
+          <t>-3,45; 11,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,09; -1,15</t>
+          <t>-6,91; 2,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 3,33</t>
+          <t>-3,25; 8,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 10,64</t>
+          <t>-3,56; 12,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,85</t>
+          <t>-10,44; -1,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 8,39</t>
+          <t>-7,21; 3,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 9,04</t>
+          <t>-1,49; 9,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 0,16</t>
+          <t>-6,57; 0,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 4,47</t>
+          <t>-3,87; 4,69</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-48,87%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>93,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-39,89%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-48,87%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>-35,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-89,2; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-43,3; 698,54</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-60,46; 549,6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 321,24</t>
+          <t>-69,27; 363,76</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-5,62</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,71</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,62</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,56</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-3,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 2,94</t>
+          <t>-10,92; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 6,24</t>
+          <t>-14,13; -0,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 3,63</t>
+          <t>-15,44; -0,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 3,62</t>
+          <t>-12,22; 2,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -0,25</t>
+          <t>-9,08; 5,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -0,42</t>
+          <t>-11,07; 4,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,99</t>
+          <t>-9,06; 1,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 1,25</t>
+          <t>-8,93; 1,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 0,41</t>
+          <t>-10,09; 0,1</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-43,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-84,07%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-85,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-50,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-18,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-31,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-43,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-84,07%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-83,2%</t>
+          <t>-33,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-61,41%</t>
+          <t>-63,03%</t>
         </is>
       </c>
     </row>
@@ -999,19 +999,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-97,51; 423,97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 385,74</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,76; 77,9</t>
+          <t>-87,26; 82,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-92,18; 65,79</t>
+          <t>-89,7; 105,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,32; 67,5</t>
+          <t>-93,22; 23,82</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,01</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,19</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,02</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,52</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,49</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 13,25</t>
+          <t>-10,13; 2,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 0,0</t>
+          <t>-8,17; 6,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 5,51</t>
+          <t>-7,72; 6,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 1,92</t>
+          <t>0,07; 14,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 6,75</t>
+          <t>-6,94; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 7,45</t>
+          <t>-4,51; 4,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,33</t>
+          <t>-3,99; 5,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,27</t>
+          <t>-5,47; 3,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 5,08</t>
+          <t>-4,79; 4,55</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-68,69%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,81%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-23,42%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>329,53%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>68,77%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-68,69%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,81%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-18,26%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,65%</t>
+          <t>-17,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-75,54; 417,37</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-79,36; 365,99</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 505,6</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,3; 449,12</t>
+          <t>-90,05; 358,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-4,55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,56</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,86</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,32</t>
+          <t>-2,51; 6,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 4,03</t>
+          <t>-1,2; 7,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,18</t>
+          <t>-1,43; 16,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,63</t>
+          <t>-9,74; 0,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,74</t>
+          <t>-6,66; 4,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 14,41</t>
+          <t>-10,29; -0,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,78</t>
+          <t>-4,74; 1,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,14</t>
+          <t>-2,85; 4,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,46</t>
+          <t>-4,29; 7,07</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>62,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>108,54%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>126,02%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-64,52%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-22,13%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-68,94%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>108,54%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>114,77%</t>
+          <t>-69,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,67%</t>
+          <t>-13,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,45</t>
+          <t>-67,8; 596,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,77; 102,3</t>
+          <t>-41,13; 764,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 20,72</t>
+          <t>-76,07; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 735,43</t>
+          <t>-92,32; 38,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 791,9</t>
+          <t>-69,15; 103,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,33; 1294,18</t>
+          <t>-100,0; 3,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 58,83</t>
+          <t>-72,44; 65,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 136,76</t>
+          <t>-44,66; 154,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,25; 191,5</t>
+          <t>-73,73; 250,84</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,34</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,24</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-6,25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,46</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-7,34</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,24</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-7,36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,06</t>
+          <t>-5,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,61</t>
+          <t>-4,8; 6,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 2,8</t>
+          <t>-9,09; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -0,61</t>
+          <t>-9,74; -0,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 6,93</t>
+          <t>-15,85; 0,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 0,0</t>
+          <t>-13,93; 2,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -0,21</t>
+          <t>-16,82; -1,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 1,81</t>
+          <t>-7,21; 1,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 0,35</t>
+          <t>-8,57; 0,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,72</t>
+          <t>-9,83; -1,62</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>32,11%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-77,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-80,56%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-65,94%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-47,12%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-77,53%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-77,87%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-76,7%</t>
+          <t>-77,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-77,94%</t>
+          <t>-79,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-94,11; 34,75</t>
+          <t>-73,15; 404,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 92,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,98</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 471,94</t>
+          <t>-94,88; 23,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,44; 85,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,67</t>
+          <t>-100,0; 46,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 53,24</t>
+          <t>-73,02; 59,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-86,67; 30,41</t>
+          <t>-85,67; 25,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-94,8; -31,08</t>
+          <t>-95,44; -33,76</t>
         </is>
       </c>
     </row>
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-9,82</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-9,46</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-9,99</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-2,26</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-5,17</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-9,82</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-9,46</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-9,99</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>-5,98</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-7,41</t>
+          <t>-7,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 7,19</t>
+          <t>-20,62; -2,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 6,3</t>
+          <t>-20,38; -1,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -1,62</t>
+          <t>-20,98; -2,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-20,98; -2,12</t>
+          <t>-8,82; 7,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 0,03</t>
+          <t>-8,62; 6,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-22,01; -2,77</t>
+          <t>-13,68; -1,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -0,3</t>
+          <t>-12,05; -0,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 0,3</t>
+          <t>-11,5; 0,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -3,06</t>
+          <t>-13,85; -3,35</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-85,49%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-82,36%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-87,04%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-43,77%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-27,33%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-85,49%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-82,36%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-87,05%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>-73,36%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-90,95%</t>
+          <t>-91,23%</t>
         </is>
       </c>
     </row>
@@ -1863,29 +1863,29 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 83,19</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 189,34</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 47,22</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; inf</t>
-        </is>
-      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,93</t>
+          <t>-100,0; 30,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-92,39; 51,83</t>
+          <t>-100,0; 47,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -17,99</t>
+          <t>-100,0; -19,2</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,91</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,05</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-3,67</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-3,71</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 0,8</t>
+          <t>-2,98; 1,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,74</t>
+          <t>-4,28; 0,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -1,26</t>
+          <t>-3,94; 2,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,67</t>
+          <t>-4,77; 0,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,2</t>
+          <t>-4,9; 0,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,0</t>
+          <t>-6,28; -1,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,51</t>
+          <t>-2,91; 0,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,2</t>
+          <t>-3,84; -0,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,37</t>
+          <t>-4,34; -0,36</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-14,76%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-40,78%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-27,75%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-32,38%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-34,71%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-62,11%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-14,76%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-40,78%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-27,52%</t>
+          <t>-62,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-45,41%</t>
+          <t>-46,17%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,6; 21,51</t>
+          <t>-50,36; 55,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,62; 19,95</t>
+          <t>-72,18; 16,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,63; -25,33</t>
+          <t>-63,77; 86,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 51,72</t>
+          <t>-63,56; 21,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 9,95</t>
+          <t>-65,68; 17,4</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-64,88; 60,65</t>
+          <t>-81,83; -25,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 12,37</t>
+          <t>-46,4; 17,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-59,48; -2,42</t>
+          <t>-59,7; -5,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,84; -3,37</t>
+          <t>-70,63; -7,62</t>
         </is>
       </c>
     </row>
